--- a/Assets/Plugins/Luban/DataTables/Datas/ItemInfo.xlsx
+++ b/Assets/Plugins/Luban/DataTables/Datas/ItemInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my projects\MiniProject\Assets\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my projects\MiniProject\Assets\Plugins\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD711002-101A-4945-AE70-E861733CDF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3181AD-DC21-475A-B027-C7EC3D6FAA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13035" yWindow="2340" windowWidth="14205" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -64,10 +64,6 @@
   </si>
   <si>
     <t>rarity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stirng</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -495,19 +491,19 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -530,13 +526,13 @@
         <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -555,22 +551,22 @@
         <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -578,19 +574,19 @@
         <v>3001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1">
         <v>10</v>
@@ -604,19 +600,19 @@
         <v>3002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1">
         <v>20</v>
